--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260910.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.53%</t>
+          <t>26.84%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.24%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.89%</t>
+          <t>7.82%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>6.22%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -748,68 +748,68 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>3.17%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,725</t>
+          <t>65,295</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>65,295</t>
+          <t>18,283</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.05%</t>
+          <t>3.07%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>18,283</t>
+          <t>19,725</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.39%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.09%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.78%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
@@ -968,51 +968,51 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>35,950</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>35,950</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
@@ -1034,46 +1034,46 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,890</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>7,890</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1100,51 +1100,51 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>19,587</t>
+          <t>125,985</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>125,985</t>
+          <t>19,587</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1166,51 +1166,51 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>9,636</t>
+          <t>51,016,112</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>51,016,112</t>
+          <t>9,636</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1293,19 +1293,19 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>444,323</t>
+          <t>807,876</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>RDI_USD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>335,499</t>
+          <t>12,628,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
